--- a/www/download/IND.value.m.mv.rpA2.xlsx
+++ b/www/download/IND.value.m.mv.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.254</t>
+          <t>2253503.86158315</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.142</t>
+          <t>2142008.46875053</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.143</t>
+          <t>2143402.88668207</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2.422</t>
+          <t>2422275.29907247</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.507</t>
+          <t>2507139.07861329</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.606</t>
+          <t>2606170.6048154</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.739</t>
+          <t>2738836.14231869</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.608</t>
+          <t>2608058.16229072</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.144</t>
+          <t>2144113.54916436</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1969551.61303861</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.817</t>
+          <t>1817255.0359717</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>1753405.31222346</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.549</t>
+          <t>1549144.98195754</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>1479292.03226316</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1556292.99069089</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.299</t>
+          <t>2298601.40502462</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>2472726.50090454</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.562</t>
+          <t>2561967.30250419</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2.601</t>
+          <t>2601429.21444609</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>2732678.16057212</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.089</t>
+          <t>3088805.12283267</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.112</t>
+          <t>3112446.06255226</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.891</t>
+          <t>2891255.69918189</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2440368.65262079</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2.253</t>
+          <t>2253249.35187951</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2.142</t>
+          <t>2142484.0880715</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2080237.07464881</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1810406.22093374</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1449232.01041395</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1469051.78709766</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.788</t>
+          <t>1787719.19717339</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.798</t>
+          <t>1798483.9401099</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>1895410.45411337</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.903</t>
+          <t>1903271.66411814</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.031</t>
+          <t>2031396.83093024</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>2250827.46392409</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2249843.4268863</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.146</t>
+          <t>2146039.34376743</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.936</t>
+          <t>1935759.24441848</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1805654.23342952</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.742</t>
+          <t>1742439.23821827</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.672</t>
+          <t>1672254.80758942</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>1502139.51157822</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>1561611.34117403</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1458048.78650936</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17.274</t>
+          <t>17273923.1374567</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.322</t>
+          <t>16321738.7062141</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.051</t>
+          <t>18050610.3347393</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15.322</t>
+          <t>15321726.6553766</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14.645</t>
+          <t>14645478.0475262</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13.182</t>
+          <t>13182112.1737392</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11.658</t>
+          <t>11657770.0561501</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10.187</t>
+          <t>10187204.726222</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8.106</t>
+          <t>8106487.67059944</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7.063</t>
+          <t>7062575.16123571</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6.549</t>
+          <t>6549112.02285126</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6.107</t>
+          <t>6106614.41769668</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.974</t>
+          <t>4973746.57868914</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.434</t>
+          <t>4433952.82645277</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.643</t>
+          <t>4643389.83491865</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.743</t>
+          <t>6743426.84193174</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.436</t>
+          <t>6435737.98126827</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.327</t>
+          <t>6327250.63197218</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6.577</t>
+          <t>6577034.27961869</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9550073.10689473</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8749974.06967635</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10.096</t>
+          <t>10095979.0511817</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.048</t>
+          <t>11048107.5093815</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10.423</t>
+          <t>10422929.6028786</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>9.309</t>
+          <t>9309110.21573174</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7.707</t>
+          <t>7707438.42660467</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6.653</t>
+          <t>6652631.53359997</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>5.627</t>
+          <t>5627244.26728057</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.909</t>
+          <t>4908752.25141387</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>5.233</t>
+          <t>5232766.54249141</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.866</t>
+          <t>2866121.26802803</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.789</t>
+          <t>2789061.05050704</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.708</t>
+          <t>2708471.68949042</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.865</t>
+          <t>2865326.02177288</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.807</t>
+          <t>2806829.13329641</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>2717803.24158648</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.879</t>
+          <t>2879207.04770186</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.702</t>
+          <t>2701673.95913805</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.431</t>
+          <t>2430804.06125384</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.309</t>
+          <t>2308651.65629386</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>2183468.45055412</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>2021225.82148047</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.803</t>
+          <t>1802836.46350754</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1725136.24219596</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1814608.86665699</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>38.922</t>
+          <t>38922267.2890821</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34.616</t>
+          <t>34615972.3362001</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.385</t>
+          <t>31384569.8168562</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29.599</t>
+          <t>29598752.7787122</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>27.519</t>
+          <t>27518761.9915404</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>24.499</t>
+          <t>24498805.0233168</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22.548</t>
+          <t>22548033.6622256</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20.959</t>
+          <t>20958593.9555853</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>19.646</t>
+          <t>19646027.1304519</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17.956</t>
+          <t>17956036.1961564</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16.139</t>
+          <t>16138703.8448059</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>14.272</t>
+          <t>14272328.7210292</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>11.554</t>
+          <t>11553675.264594</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>9.491</t>
+          <t>9491369.9421454</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9039944.68643869</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.919</t>
+          <t>4918717.13750592</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5.034</t>
+          <t>5034006.10572357</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4.935</t>
+          <t>4935411.46317363</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4.793</t>
+          <t>4792863.64863736</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.427</t>
+          <t>5427097.81739643</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5570054.86280775</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5.641</t>
+          <t>5641292.57584914</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5.225</t>
+          <t>5224812.75199865</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4.516</t>
+          <t>4516288.80976379</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3950315.57589924</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3.213</t>
+          <t>3212647.74332211</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3009817.30712156</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2570164.19165953</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.817</t>
+          <t>2817259.38272226</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2.128</t>
+          <t>2128349.07528259</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8.891</t>
+          <t>8891049.94609716</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.254</t>
+          <t>8253856.64079508</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.972</t>
+          <t>8972326.49351424</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8.263</t>
+          <t>8262888.4758231</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.396</t>
+          <t>8396007.11531002</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8.369</t>
+          <t>8369298.56514238</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7.766</t>
+          <t>7765729.51048762</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6.715</t>
+          <t>6714925.82808576</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5.438</t>
+          <t>5438167.93451891</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4.563</t>
+          <t>4563065.81501924</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4.217</t>
+          <t>4216812.21139578</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>3.834</t>
+          <t>3834443.46315397</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3179703.09729171</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.521</t>
+          <t>2521301.54208314</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>2764192.54956354</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>2090915.55394235</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.049</t>
+          <t>2049271.47081113</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>2212348.99014684</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2.273</t>
+          <t>2273224.80970465</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.385</t>
+          <t>2385109.59641337</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.722</t>
+          <t>2721895.11872437</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.653</t>
+          <t>2652885.5386178</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.534</t>
+          <t>2534408.96493498</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.245</t>
+          <t>2244643.00325704</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.076</t>
+          <t>2075899.42221553</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2.003</t>
+          <t>2002602.90011232</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.937</t>
+          <t>1937395.45700913</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>1737225.21520885</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1397615.59225702</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1463598.36195738</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>2158423.76403634</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.133</t>
+          <t>2132501.83967435</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>2503548.38404822</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2.313</t>
+          <t>2312758.75730406</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2229730.25823153</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2370153.13943201</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.474</t>
+          <t>2473587.61528472</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.281</t>
+          <t>2281447.76736749</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.035</t>
+          <t>2035384.68257457</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.866</t>
+          <t>1866086.01543016</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>1742984.19415581</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1617442.07856164</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1395825.79866158</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>1213034.61973092</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1253929.61904411</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.309</t>
+          <t>2308551.99971831</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.331</t>
+          <t>2330881.69955184</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.508</t>
+          <t>2507899.41413964</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2620049.95230006</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.866</t>
+          <t>2865531.74572024</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.298</t>
+          <t>3298365.08784878</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.194</t>
+          <t>3193852.67625579</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.999</t>
+          <t>2999219.44546614</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.485</t>
+          <t>2484898.2057093</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.252</t>
+          <t>2252199.90806858</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2.168</t>
+          <t>2168240.53350093</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>2091051.85931453</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1850124.41543693</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1554920.34501631</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1493817.57917544</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.854</t>
+          <t>19853981.5226097</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16.114</t>
+          <t>16114047.447736</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.249</t>
+          <t>16249345.7691156</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.313</t>
+          <t>13313053.6081699</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11.868</t>
+          <t>11867906.6748302</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12.115</t>
+          <t>12114920.2262841</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11.714</t>
+          <t>11713763.7286041</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.334</t>
+          <t>10334404.5425352</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8.309</t>
+          <t>8309235.94028095</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7.482</t>
+          <t>7481951.20383457</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>6.341</t>
+          <t>6341138.83209846</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>5.481</t>
+          <t>5480799.63970609</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>4.236</t>
+          <t>4236415.64351478</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.745</t>
+          <t>3745126.48420935</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4.153</t>
+          <t>4153446.86515763</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>2523451.50640115</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2530399.0414041</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.612</t>
+          <t>2612284.89797634</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.701</t>
+          <t>2700785.75981199</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.983</t>
+          <t>2983340.92070201</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.093</t>
+          <t>3093321.9674836</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.004</t>
+          <t>3004239.42141564</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.827</t>
+          <t>2827292.07214811</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.482</t>
+          <t>2481800.68609603</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>2180723.17951848</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>2122890.31320818</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.014</t>
+          <t>2013527.48070408</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>1705120.77982013</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1445306.67418341</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1424897.8617223</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.894</t>
+          <t>1893976.9248849</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.912</t>
+          <t>1912263.74438566</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>1968851.17379603</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1989960.47808978</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.098</t>
+          <t>2098283.40732725</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.313</t>
+          <t>2313126.96714346</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2320364.31298033</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>2183003.94324396</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>1883390.73609238</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.722</t>
+          <t>1721803.54123577</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.682</t>
+          <t>1681911.86497405</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1604341.84298745</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>1434113.55191079</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1210681.89991744</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1191082.76562589</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.447</t>
+          <t>2446600.19620342</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.391</t>
+          <t>2391296.92082855</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.218</t>
+          <t>2217891.41944624</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2170092.92947845</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.211</t>
+          <t>2210800.5949645</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2279769.61140736</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2320277.31604314</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.168</t>
+          <t>2167574.02817551</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>1953700.57057312</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>1718664.14584193</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1636139.00225638</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1554846.84920569</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1385359.18657786</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.294</t>
+          <t>1294329.41877869</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1479698.64980346</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.768</t>
+          <t>3768237.38665731</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.788</t>
+          <t>3788050.57701356</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3919661.10960652</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4.137</t>
+          <t>4137089.99075402</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4.073</t>
+          <t>4072833.04215336</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.835</t>
+          <t>4835451.50755593</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.462</t>
+          <t>4461850.42334551</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4049825.75596463</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>3239277.63036677</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.932</t>
+          <t>2931871.15941758</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.711</t>
+          <t>2711453.4701736</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.706</t>
+          <t>2706054.16037076</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.401</t>
+          <t>2400548.20198479</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>2122917.66438872</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.242</t>
+          <t>2242013.59557618</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10.194</t>
+          <t>10194288.6486836</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.814</t>
+          <t>9813659.39542524</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.489</t>
+          <t>9488927.71008445</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9.491</t>
+          <t>9491351.99937971</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10.201</t>
+          <t>10201283.6143787</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10.176</t>
+          <t>10175538.0193575</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8.754</t>
+          <t>8753938.04114836</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>7580262.19225504</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6.232</t>
+          <t>6231955.78830269</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.959</t>
+          <t>4959140.75839207</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.618</t>
+          <t>4617592.26602999</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.431</t>
+          <t>4431291.89782613</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3.788</t>
+          <t>3787959.34022019</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.843</t>
+          <t>2843029.47307017</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.466</t>
+          <t>3466029.31441497</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19.622</t>
+          <t>19621778.3438613</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18.342</t>
+          <t>18341518.0400962</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17.805</t>
+          <t>17804943.7825021</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>45.633</t>
+          <t>45632682.2016954</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29.598</t>
+          <t>29597556.5343985</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25.143</t>
+          <t>25143284.4553111</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>26.093</t>
+          <t>26093216.5382118</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>23439816.2897026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19830208.71915</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20199549.2998833</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17.172</t>
+          <t>17172411.3718135</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>12.386</t>
+          <t>12386235.3858654</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>10.356</t>
+          <t>10356207.5191416</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>9.086</t>
+          <t>9086479.5117246</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>8.941</t>
+          <t>8941173.41281774</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>52.466</t>
+          <t>52466406.6751629</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>51.825</t>
+          <t>51824825.1529721</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>48.735</t>
+          <t>48734716.4990409</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>48.583</t>
+          <t>48583386.5616866</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>47.335</t>
+          <t>47335130.1306447</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>49.263</t>
+          <t>49263142.3456069</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>53.007</t>
+          <t>53007191.2972161</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>52.513</t>
+          <t>52512572.3553632</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48899575.8069296</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>44.223</t>
+          <t>44222842.3826175</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>38.474</t>
+          <t>38474464.2921193</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>33.795</t>
+          <t>33795261.9566453</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>26.746</t>
+          <t>26745714.6754036</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>25.434</t>
+          <t>25434295.8657166</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>25.821</t>
+          <t>25821033.9235991</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2.755</t>
+          <t>2754551.1665793</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.657</t>
+          <t>2656606.01425481</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.508</t>
+          <t>2508370.96876147</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2.498</t>
+          <t>2498000.97779273</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.597</t>
+          <t>2596826.77785069</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>2704666.29775386</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.616</t>
+          <t>2615930.98326735</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2.368</t>
+          <t>2368128.90816484</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2.008</t>
+          <t>2007864.64381653</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.859</t>
+          <t>1859315.14840681</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.776</t>
+          <t>1776163.43320658</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1.631</t>
+          <t>1630596.47032836</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1511850.38340856</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1450775.54758396</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1645646.73499942</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.128</t>
+          <t>2127885.85143704</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.005</t>
+          <t>2005028.04125136</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>2018305.77167398</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2.075</t>
+          <t>2075061.41095187</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>2240986.15123089</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2509538.17766998</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>2479151.21351691</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.358</t>
+          <t>2358008.36759668</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.052</t>
+          <t>2051556.33181392</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1876854.0349889</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>1804604.07297134</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1.838</t>
+          <t>1838352.89893922</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>1611014.4586664</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1315937.26140791</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1323831.27913801</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2129630.52088187</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>2365007.8767138</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2530428.45410966</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.626</t>
+          <t>2626245.30086201</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.488</t>
+          <t>2488121.91617994</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.441</t>
+          <t>2441244.92023475</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.779</t>
+          <t>2779059.38760109</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.848</t>
+          <t>2848192.0419619</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.732</t>
+          <t>2732099.16110322</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.599</t>
+          <t>2599047.65954383</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.583</t>
+          <t>2583393.1144601</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.724</t>
+          <t>2724308.63108703</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.609</t>
+          <t>2608893.63559279</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.359</t>
+          <t>2359288.12276846</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.203</t>
+          <t>2203245.92328761</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7.102</t>
+          <t>7101714.95467379</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6.716</t>
+          <t>6716052.66293862</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.159</t>
+          <t>7158601.29170152</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9210272.84700668</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8.045</t>
+          <t>8045134.32213271</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7.685</t>
+          <t>7685435.94649012</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8.294</t>
+          <t>8294490.75030679</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7.699</t>
+          <t>7699062.15921823</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7.157</t>
+          <t>7156864.17125621</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6.621</t>
+          <t>6621232.09377928</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5.514</t>
+          <t>5513987.76929995</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5.035</t>
+          <t>5035272.24795083</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4.455</t>
+          <t>4454605.98586653</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>4.551</t>
+          <t>4551049.03990639</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5010416.7092413</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23.263</t>
+          <t>23262654.1341633</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18.641</t>
+          <t>18640878.7902145</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.478</t>
+          <t>15478161.8547628</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14.112</t>
+          <t>14111900.5586227</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14.382</t>
+          <t>14382374.8823997</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14.024</t>
+          <t>14024042.566014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12.802</t>
+          <t>12801616.9200306</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11.348</t>
+          <t>11348273.805344</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9280429.60793768</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>7332763.20824603</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>6.743</t>
+          <t>6742703.7381126</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5.908</t>
+          <t>5908017.39377529</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>4.941</t>
+          <t>4941485.37361125</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>4226833.49673512</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4.971</t>
+          <t>4971088.49478632</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1616234.06465721</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1469840.95106191</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1491888.06254946</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1557894.84597218</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1545665.7859681</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1750017.93673713</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1636362.59333603</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1519577.77203032</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1329895.26880463</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>1298693.32881731</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1325676.80294911</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.229</t>
+          <t>1228709.64119738</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>1043928.02563831</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>928042.288927206</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>1134268.63147562</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17.957</t>
+          <t>17957399.7936929</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15.049</t>
+          <t>15048534.414071</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13.149</t>
+          <t>13149020.9435116</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12.143</t>
+          <t>12143151.4944935</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12.346</t>
+          <t>12346324.6818159</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10.853</t>
+          <t>10853246.4449202</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9.605</t>
+          <t>9604635.075378</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>9.339</t>
+          <t>9339201.88050262</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>7.772</t>
+          <t>7771931.70109619</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>6.659</t>
+          <t>6658761.2559044</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5.883</t>
+          <t>5882855.19853814</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4.895</t>
+          <t>4894515.38942976</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>3875966.46234291</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3319837.27918553</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3.429</t>
+          <t>3429006.38133129</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9.579</t>
+          <t>9578588.24935994</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.675</t>
+          <t>8674733.86270657</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7.393</t>
+          <t>7392854.02435677</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7.373</t>
+          <t>7373163.54057077</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6.927</t>
+          <t>6926689.94202266</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6.231</t>
+          <t>6230781.92848946</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.102</t>
+          <t>6102367.80961405</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5879731.39655699</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>6.168</t>
+          <t>6167586.66505664</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>6.083</t>
+          <t>6083082.214734</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>5.547</t>
+          <t>5546984.24452394</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>5.064</t>
+          <t>5064170.97330397</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>4.683</t>
+          <t>4682675.52860823</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>4.791</t>
+          <t>4790559.66195619</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>5.805</t>
+          <t>5805036.94533039</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>3406980.18758809</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.348</t>
+          <t>3348310.59971034</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.996</t>
+          <t>2995589.39669276</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.967</t>
+          <t>2966971.88158328</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3.278</t>
+          <t>3277993.75794695</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3520358.70511287</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.158</t>
+          <t>3157772.73017163</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3.071</t>
+          <t>3071288.07588457</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2.717</t>
+          <t>2716903.85594805</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2.459</t>
+          <t>2458517.59167052</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2.161</t>
+          <t>2161433.03238353</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2.418</t>
+          <t>2418256.84132921</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>2018073.55550392</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1.864</t>
+          <t>1864476.58469023</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.966</t>
+          <t>1965864.05979458</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2.269</t>
+          <t>2269027.9652541</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.366</t>
+          <t>2366452.29463799</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.442</t>
+          <t>2441600.10373689</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2.579</t>
+          <t>2578828.43419579</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.757</t>
+          <t>2757471.95229435</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2.821</t>
+          <t>2821290.01875454</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2.818</t>
+          <t>2818399.19484521</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2469922.66548209</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2.331</t>
+          <t>2331254.18892214</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2.151</t>
+          <t>2151309.04757937</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2.089</t>
+          <t>2089121.79739102</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1959785.75298399</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1751296.31551647</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1530439.13323619</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1582010.47843236</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10.632</t>
+          <t>10632078.0386781</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9.757</t>
+          <t>9756897.42845429</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.692</t>
+          <t>9692043.30482081</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9.063</t>
+          <t>9063343.07488521</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.427</t>
+          <t>9426593.73621722</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9.004</t>
+          <t>9004144.38841259</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>7820402.26779621</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>7.227</t>
+          <t>7227306.02301919</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6.588</t>
+          <t>6587552.08547725</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5649886.39057701</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>5.096</t>
+          <t>5096465.44329546</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.658</t>
+          <t>4658073.50969081</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.951</t>
+          <t>3951298.82745926</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.159</t>
+          <t>3158637.05146223</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3809980.52484177</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3.338</t>
+          <t>3337808.1245187</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.138</t>
+          <t>3137975.85530269</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.102</t>
+          <t>3102283.71488913</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>3173361.24500982</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.252</t>
+          <t>3251587.01971313</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3669588.50614195</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.679</t>
+          <t>3678738.51537092</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3.384</t>
+          <t>3384142.15093845</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.911</t>
+          <t>2911328.44006297</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2.647</t>
+          <t>2647185.84877918</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2.496</t>
+          <t>2496145.28043852</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2.322</t>
+          <t>2321662.52639849</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2.084</t>
+          <t>2083553.0783474</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1.982</t>
+          <t>1982441.73111148</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.752</t>
+          <t>1752094.64826792</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16300306.2759229</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15.346</t>
+          <t>15345864.8727196</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14.646</t>
+          <t>14646164.1773322</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>12.758</t>
+          <t>12757902.8779274</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>14860351.601295</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>14.154</t>
+          <t>14154183.4847741</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12.688</t>
+          <t>12687760.3713827</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11.309</t>
+          <t>11309144.8371299</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>9.268</t>
+          <t>9267818.65761898</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7.061</t>
+          <t>7060756.10390742</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5750418.63729243</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>4.974</t>
+          <t>4974044.90096201</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>3.757</t>
+          <t>3757391.1415427</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>3.212</t>
+          <t>3211997.13396554</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>3.925</t>
+          <t>3924831.82094994</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>26.83</t>
+          <t>26830244.8521814</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20.936</t>
+          <t>20936390.398622</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.388</t>
+          <t>19387805.2162063</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>24.136</t>
+          <t>24136171.0946166</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>40.268</t>
+          <t>40268464.6087094</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>32509714.1780935</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>27.488</t>
+          <t>27488213.1556183</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>24.482</t>
+          <t>24481889.4583927</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>20.939</t>
+          <t>20939239.3830616</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>15.689</t>
+          <t>15689442.5594899</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>12.792</t>
+          <t>12791751.3894877</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>9.951</t>
+          <t>9951396.0859971</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>7.815</t>
+          <t>7815425.38852875</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>6.233</t>
+          <t>6232700.3220964</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>7.951</t>
+          <t>7951287.66436853</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11110319.5050898</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10.379</t>
+          <t>10378946.1845602</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>9.772</t>
+          <t>9772401.23712986</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>9.055</t>
+          <t>9054648.65265102</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10.005</t>
+          <t>10005261.0549007</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9.603</t>
+          <t>9602956.00854618</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9.178</t>
+          <t>9178269.61684327</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>7.751</t>
+          <t>7751469.05198595</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>5.946</t>
+          <t>5945927.11985315</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>5.199</t>
+          <t>5198526.28670237</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4.887</t>
+          <t>4887083.01978389</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>4.422</t>
+          <t>4422379.67802996</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3640105.80351971</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>4.078</t>
+          <t>4077730.11587218</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>4.631</t>
+          <t>4630837.46169239</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5.001</t>
+          <t>5000826.77998642</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.887</t>
+          <t>4886822.18448519</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.751</t>
+          <t>4750691.99449258</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4.672</t>
+          <t>4671621.0713492</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4.931</t>
+          <t>4930795.35859703</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5.299</t>
+          <t>5299279.96759229</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5.155</t>
+          <t>5154736.12176177</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4.816</t>
+          <t>4815560.85444978</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4.322</t>
+          <t>4321522.29500919</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>3.782</t>
+          <t>3781569.29003648</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>3.536</t>
+          <t>3535877.75849883</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3349585.02692611</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2.821</t>
+          <t>2821202.89325477</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2.699</t>
+          <t>2699418.29157991</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2.889</t>
+          <t>2888607.03427084</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>2255553.87224114</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>2015271.2997744</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2.097</t>
+          <t>2097138.31735506</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2.185</t>
+          <t>2185383.27269699</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.246</t>
+          <t>2246065.0848717</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>2450974.7732884</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2.525</t>
+          <t>2525137.13793645</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2.316</t>
+          <t>2315588.65503324</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2.007</t>
+          <t>2007293.41717493</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1.791</t>
+          <t>1791199.77045022</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1.759</t>
+          <t>1759430.30504615</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1638162.22551117</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1464370.51591402</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1238915.97300408</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1277925.91301482</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5.586</t>
+          <t>5586268.81669096</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5.515</t>
+          <t>5515075.49432339</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5.524</t>
+          <t>5524451.74827682</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5469510.7178199</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>5.863</t>
+          <t>5862986.20933506</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5710304.25080494</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>7.146</t>
+          <t>7145941.01989042</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6.673</t>
+          <t>6673447.9438125</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>5.399</t>
+          <t>5398710.1727759</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>4.534</t>
+          <t>4534173.47024936</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>3.997</t>
+          <t>3997229.31723308</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>3.765</t>
+          <t>3764990.75293201</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>3.167</t>
+          <t>3167421.58079506</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2.748</t>
+          <t>2747891.787503</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2.976</t>
+          <t>2975926.81689461</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5.541</t>
+          <t>5541275.48743021</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5.404</t>
+          <t>5403775.27222669</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>5320383.06600722</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>5.911</t>
+          <t>5910637.97440578</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>5.683</t>
+          <t>5683361.17350531</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5.741</t>
+          <t>5740542.99593407</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6.143</t>
+          <t>6143404.99246545</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6.384</t>
+          <t>6384051.07925199</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6310329.76400997</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>6.101</t>
+          <t>6101111.71369096</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>5.697</t>
+          <t>5697024.66937219</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>5.538</t>
+          <t>5537806.89056663</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5259506.4546303</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>5.045</t>
+          <t>5044934.98142315</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>5.189</t>
+          <t>5189145.87937189</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2.716</t>
+          <t>2715877.64093158</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2599674.26871398</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2.493</t>
+          <t>2493232.13727932</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2.482</t>
+          <t>2482452.61111557</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>2478862.25979682</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.487</t>
+          <t>2486717.34075303</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.421</t>
+          <t>2420950.72117064</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.384</t>
+          <t>2383741.30215885</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2260411.86971817</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>2211939.44893942</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2.139</t>
+          <t>2138756.83350249</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2059858.57078666</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1908639.02639897</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1.836</t>
+          <t>1836101.17707021</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1810276.35294746</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>17.381</t>
+          <t>17380843.6736083</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>17.416</t>
+          <t>17416026.508201</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17.801</t>
+          <t>17801258.6375186</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>18.827</t>
+          <t>18826511.737941</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19.033</t>
+          <t>19033206.2380059</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>19.528</t>
+          <t>19527523.4465163</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20.848</t>
+          <t>20847837.7221798</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>21.163</t>
+          <t>21162629.1748837</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>20.347</t>
+          <t>20346606.8732875</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>19.258</t>
+          <t>19257628.9491272</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>17.581</t>
+          <t>17581027.6362526</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>16.167</t>
+          <t>16167365.3379799</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>14.328</t>
+          <t>14328336.5124031</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>12.471</t>
+          <t>12471294.5218392</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>13.962</t>
+          <t>13962314.72264</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>384.178</t>
+          <t>384178012.561611</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>353.776</t>
+          <t>353776472.335316</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>340.953</t>
+          <t>340952514.646113</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>364.443</t>
+          <t>364443040.708422</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>368.118</t>
+          <t>368118092.316633</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>353.339</t>
+          <t>353339371.857031</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>346.065</t>
+          <t>346065482.74496</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>324.181</t>
+          <t>324180856.896607</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>286.518</t>
+          <t>286518144.098807</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>255.652</t>
+          <t>255651936.250759</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>227.54</t>
+          <t>227540323.596278</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>202.569</t>
+          <t>202568518.812846</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>170.301</t>
+          <t>170300715.852923</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>152.775</t>
+          <t>152774946.623182</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>162.281</t>
+          <t>162281011.545621</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
